--- a/Codelist Excel Files and Conversion Templates to XML/mwd_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/mwd_properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EC0F42-55F4-D84D-97D1-AFEE5C4B3631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E62D0BE-A220-744B-977F-FE40B1BD35D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7100" yWindow="2960" windowWidth="38400" windowHeight="20980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="389">
   <si>
     <t>Start</t>
   </si>
@@ -1201,13 +1201,16 @@
   </si>
   <si>
     <t>Nvalue (-)</t>
+  </si>
+  <si>
+    <t>(mass per time) per area</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1311,6 +1314,12 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1383,7 +1392,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1467,6 +1476,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2840,8 +2852,8 @@
       <c r="E33" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="14" t="s">
-        <v>94</v>
+      <c r="F33" s="34" t="s">
+        <v>388</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>140</v>
